--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260914.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260914.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.27%</t>
+          <t>10.18%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.16%</t>
+          <t>9.15%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.54%</t>
+          <t>8.53%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.10%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.13%</t>
+          <t>7.10%</t>
         </is>
       </c>
     </row>
@@ -726,51 +726,51 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.31%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,546,000</t>
+          <t>2,512,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.27%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,477,000</t>
+          <t>2,546,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.14%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.91%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.58%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.38%</t>
+          <t>4.37%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.23%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>372,000</t>
+          <t>413,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>637,000</t>
+          <t>446,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1144,68 +1144,68 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>3,248,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>3,248,000</t>
+          <t>485,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>501,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,34 +1327,34 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>501,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>4,316,476,572</t>
+          <t>4,823,473,398</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,904,064,338</t>
+          <t>1,848,386,338</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>768,318,830</t>
+          <t>443,464,120</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,208,109,900</t>
+          <t>1,258,097,300</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
